--- a/tmp/column_naming_test.xlsx
+++ b/tmp/column_naming_test.xlsx
@@ -1125,7 +1125,7 @@
         <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>21000</v>
+        <v>21800</v>
       </c>
     </row>
     <row r="4">
@@ -1159,7 +1159,7 @@
         <v>94</v>
       </c>
       <c r="J4" t="n">
-        <v>13400</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="5">
@@ -1193,7 +1193,7 @@
         <v>105</v>
       </c>
       <c r="J5" t="n">
-        <v>9200</v>
+        <v>9500</v>
       </c>
     </row>
   </sheetData>
